--- a/00-esmagadora-modelo/dados_sujos/apontamentos_mensais/producao_2025_06.xlsx
+++ b/00-esmagadora-modelo/dados_sujos/apontamentos_mensais/producao_2025_06.xlsx
@@ -480,25 +480,25 @@
         <v>45809</v>
       </c>
       <c r="B5" t="n">
-        <v>1501.64</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1094.53</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>303.23</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>2131</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>362012</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>68636</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -506,25 +506,25 @@
         <v>45810</v>
       </c>
       <c r="B6" t="n">
-        <v>1450.93</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1056.28</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>282.06</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1981</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>402539</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>63883</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -532,25 +532,25 @@
         <v>45811</v>
       </c>
       <c r="B7" t="n">
-        <v>1475.13</v>
+        <v>1519.66</v>
       </c>
       <c r="C7" t="n">
-        <v>23.67</v>
+        <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>1069.52</v>
+        <v>1111.22</v>
       </c>
       <c r="E7" t="n">
-        <v>293.54</v>
+        <v>300.83</v>
       </c>
       <c r="F7" t="n">
-        <v>2520</v>
+        <v>1338</v>
       </c>
       <c r="G7" t="n">
-        <v>389534</v>
+        <v>379135</v>
       </c>
       <c r="H7" t="n">
-        <v>66230</v>
+        <v>70932</v>
       </c>
     </row>
     <row r="8">
@@ -558,25 +558,25 @@
         <v>45812</v>
       </c>
       <c r="B8" t="n">
-        <v>1494.84</v>
+        <v>1332.93</v>
       </c>
       <c r="C8" t="n">
-        <v>24</v>
+        <v>21.84</v>
       </c>
       <c r="D8" t="n">
-        <v>1074.61</v>
+        <v>969.83</v>
       </c>
       <c r="E8" t="n">
-        <v>293.94</v>
+        <v>263.12</v>
       </c>
       <c r="F8" t="n">
-        <v>2020</v>
+        <v>1157</v>
       </c>
       <c r="G8" t="n">
-        <v>401714</v>
+        <v>343074</v>
       </c>
       <c r="H8" t="n">
-        <v>67047</v>
+        <v>61225</v>
       </c>
     </row>
     <row r="9">
@@ -584,25 +584,25 @@
         <v>45813</v>
       </c>
       <c r="B9" t="n">
-        <v>1228.3</v>
+        <v>1179.81</v>
       </c>
       <c r="C9" t="n">
-        <v>20.18</v>
+        <v>20.28</v>
       </c>
       <c r="D9" t="n">
-        <v>886.15</v>
+        <v>854.29</v>
       </c>
       <c r="E9" t="n">
-        <v>239.27</v>
+        <v>235.69</v>
       </c>
       <c r="F9" t="n">
-        <v>1679</v>
+        <v>881</v>
       </c>
       <c r="G9" t="n">
-        <v>333259</v>
+        <v>313655</v>
       </c>
       <c r="H9" t="n">
-        <v>53939</v>
+        <v>52437</v>
       </c>
     </row>
     <row r="10">
@@ -610,25 +610,25 @@
         <v>45814</v>
       </c>
       <c r="B10" t="n">
-        <v>1504.08</v>
+        <v>1418.72</v>
       </c>
       <c r="C10" t="n">
-        <v>24</v>
+        <v>22.18</v>
       </c>
       <c r="D10" t="n">
-        <v>1092.43</v>
+        <v>1021.17</v>
       </c>
       <c r="E10" t="n">
-        <v>285.65</v>
+        <v>276.34</v>
       </c>
       <c r="F10" t="n">
-        <v>2271</v>
+        <v>1357</v>
       </c>
       <c r="G10" t="n">
-        <v>394891</v>
+        <v>373572</v>
       </c>
       <c r="H10" t="n">
-        <v>68354</v>
+        <v>68608</v>
       </c>
     </row>
     <row r="11">
@@ -636,25 +636,25 @@
         <v>45815</v>
       </c>
       <c r="B11" t="n">
-        <v>1471.65</v>
+        <v>1530.11</v>
       </c>
       <c r="C11" t="n">
         <v>24</v>
       </c>
       <c r="D11" t="n">
-        <v>1075.84</v>
+        <v>1105.14</v>
       </c>
       <c r="E11" t="n">
-        <v>285.73</v>
+        <v>310.53</v>
       </c>
       <c r="F11" t="n">
-        <v>2147</v>
+        <v>1594</v>
       </c>
       <c r="G11" t="n">
-        <v>374672</v>
+        <v>392100</v>
       </c>
       <c r="H11" t="n">
-        <v>65389</v>
+        <v>65659</v>
       </c>
     </row>
     <row r="12">
@@ -662,25 +662,25 @@
         <v>45816</v>
       </c>
       <c r="B12" t="n">
-        <v>1536.75</v>
+        <v>938.35</v>
       </c>
       <c r="C12" t="n">
-        <v>24</v>
+        <v>14.8</v>
       </c>
       <c r="D12" t="n">
-        <v>1126.77</v>
+        <v>685.04</v>
       </c>
       <c r="E12" t="n">
-        <v>309.09</v>
+        <v>179.99</v>
       </c>
       <c r="F12" t="n">
-        <v>2702</v>
+        <v>912</v>
       </c>
       <c r="G12" t="n">
-        <v>410360</v>
+        <v>251344</v>
       </c>
       <c r="H12" t="n">
-        <v>64600</v>
+        <v>42474</v>
       </c>
     </row>
     <row r="13">
@@ -688,25 +688,25 @@
         <v>45817</v>
       </c>
       <c r="B13" t="n">
-        <v>1525.88</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1106.14</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>303.3</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>2557</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>402743</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>67423</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -714,25 +714,25 @@
         <v>45818</v>
       </c>
       <c r="B14" t="n">
-        <v>1054.59</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>761.4400000000001</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>208.25</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1904</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>282948</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>49057</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -740,25 +740,25 @@
         <v>45819</v>
       </c>
       <c r="B15" t="n">
-        <v>659.67</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>10.05</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>475.33</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>133.34</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1074</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>201594</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>29357</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -766,25 +766,25 @@
         <v>45820</v>
       </c>
       <c r="B16" t="n">
-        <v>811.54</v>
+        <v>1429.17</v>
       </c>
       <c r="C16" t="n">
-        <v>13.73</v>
+        <v>24</v>
       </c>
       <c r="D16" t="n">
-        <v>588.83</v>
+        <v>1036.39</v>
       </c>
       <c r="E16" t="n">
-        <v>165.01</v>
+        <v>284.34</v>
       </c>
       <c r="F16" t="n">
-        <v>1660</v>
+        <v>1622</v>
       </c>
       <c r="G16" t="n">
-        <v>247601</v>
+        <v>397010</v>
       </c>
       <c r="H16" t="n">
-        <v>36196</v>
+        <v>58509</v>
       </c>
     </row>
     <row r="17">
@@ -792,25 +792,25 @@
         <v>45821</v>
       </c>
       <c r="B17" t="n">
-        <v>1602.52</v>
+        <v>1481.32</v>
       </c>
       <c r="C17" t="n">
         <v>24</v>
       </c>
       <c r="D17" t="n">
-        <v>1165.88</v>
+        <v>1079.29</v>
       </c>
       <c r="E17" t="n">
-        <v>323.02</v>
+        <v>293.74</v>
       </c>
       <c r="F17" t="n">
-        <v>2098</v>
+        <v>1793</v>
       </c>
       <c r="G17" t="n">
-        <v>401930</v>
+        <v>383562</v>
       </c>
       <c r="H17" t="n">
-        <v>69766</v>
+        <v>65484</v>
       </c>
     </row>
     <row r="18">
@@ -818,25 +818,25 @@
         <v>45822</v>
       </c>
       <c r="B18" t="n">
-        <v>1297.19</v>
+        <v>1346.93</v>
       </c>
       <c r="C18" t="n">
-        <v>22.08</v>
+        <v>21.98</v>
       </c>
       <c r="D18" t="n">
-        <v>940.55</v>
+        <v>969.76</v>
       </c>
       <c r="E18" t="n">
-        <v>260.63</v>
+        <v>268.52</v>
       </c>
       <c r="F18" t="n">
-        <v>1763</v>
+        <v>1430</v>
       </c>
       <c r="G18" t="n">
-        <v>348974</v>
+        <v>372163</v>
       </c>
       <c r="H18" t="n">
-        <v>60237</v>
+        <v>60660</v>
       </c>
     </row>
     <row r="19">
@@ -844,25 +844,25 @@
         <v>45823</v>
       </c>
       <c r="B19" t="n">
-        <v>1528.91</v>
+        <v>1478.93</v>
       </c>
       <c r="C19" t="n">
-        <v>24</v>
+        <v>23.07</v>
       </c>
       <c r="D19" t="n">
-        <v>1098.65</v>
+        <v>1071.95</v>
       </c>
       <c r="E19" t="n">
-        <v>296.28</v>
+        <v>294.41</v>
       </c>
       <c r="F19" t="n">
-        <v>2344</v>
+        <v>1358</v>
       </c>
       <c r="G19" t="n">
-        <v>426697</v>
+        <v>395093</v>
       </c>
       <c r="H19" t="n">
-        <v>67223</v>
+        <v>66321</v>
       </c>
     </row>
     <row r="20">
@@ -870,25 +870,25 @@
         <v>45824</v>
       </c>
       <c r="B20" t="n">
-        <v>1396.14</v>
+        <v>1483.94</v>
       </c>
       <c r="C20" t="n">
-        <v>22.91</v>
+        <v>24</v>
       </c>
       <c r="D20" t="n">
-        <v>1012.21</v>
+        <v>1075.25</v>
       </c>
       <c r="E20" t="n">
-        <v>290.61</v>
+        <v>290.85</v>
       </c>
       <c r="F20" t="n">
-        <v>1741</v>
+        <v>1421</v>
       </c>
       <c r="G20" t="n">
-        <v>389088</v>
+        <v>410707</v>
       </c>
       <c r="H20" t="n">
-        <v>56852</v>
+        <v>69345</v>
       </c>
     </row>
     <row r="21">
@@ -896,25 +896,25 @@
         <v>45825</v>
       </c>
       <c r="B21" t="n">
-        <v>1449.14</v>
+        <v>1318.75</v>
       </c>
       <c r="C21" t="n">
-        <v>24</v>
+        <v>21.71</v>
       </c>
       <c r="D21" t="n">
-        <v>1054.05</v>
+        <v>952.34</v>
       </c>
       <c r="E21" t="n">
-        <v>282.59</v>
+        <v>265.19</v>
       </c>
       <c r="F21" t="n">
-        <v>2745</v>
+        <v>1464</v>
       </c>
       <c r="G21" t="n">
-        <v>392674</v>
+        <v>344633</v>
       </c>
       <c r="H21" t="n">
-        <v>70500</v>
+        <v>56816</v>
       </c>
     </row>
     <row r="22">
@@ -922,25 +922,25 @@
         <v>45826</v>
       </c>
       <c r="B22" t="n">
-        <v>1495.02</v>
+        <v>1488.38</v>
       </c>
       <c r="C22" t="n">
         <v>24</v>
       </c>
       <c r="D22" t="n">
-        <v>1080.39</v>
+        <v>1074.18</v>
       </c>
       <c r="E22" t="n">
-        <v>303.05</v>
+        <v>293.84</v>
       </c>
       <c r="F22" t="n">
-        <v>2222</v>
+        <v>1284</v>
       </c>
       <c r="G22" t="n">
-        <v>403516</v>
+        <v>379680</v>
       </c>
       <c r="H22" t="n">
-        <v>65647</v>
+        <v>70083</v>
       </c>
     </row>
     <row r="23">
@@ -948,25 +948,25 @@
         <v>45827</v>
       </c>
       <c r="B23" t="n">
-        <v>781.35</v>
+        <v>750.73</v>
       </c>
       <c r="C23" t="n">
         <v>12.48</v>
       </c>
       <c r="D23" t="n">
-        <v>570.4</v>
+        <v>540.22</v>
       </c>
       <c r="E23" t="n">
-        <v>153.87</v>
+        <v>149.43</v>
       </c>
       <c r="F23" t="n">
-        <v>1413</v>
+        <v>722</v>
       </c>
       <c r="G23" t="n">
-        <v>219897</v>
+        <v>197340</v>
       </c>
       <c r="H23" t="n">
-        <v>37541</v>
+        <v>32843</v>
       </c>
     </row>
     <row r="24">
@@ -974,25 +974,25 @@
         <v>45828</v>
       </c>
       <c r="B24" t="n">
-        <v>1464.72</v>
+        <v>1300.46</v>
       </c>
       <c r="C24" t="n">
-        <v>24</v>
+        <v>20.84</v>
       </c>
       <c r="D24" t="n">
-        <v>1069.59</v>
+        <v>947.91</v>
       </c>
       <c r="E24" t="n">
-        <v>289.81</v>
+        <v>261.6</v>
       </c>
       <c r="F24" t="n">
-        <v>2253</v>
+        <v>1117</v>
       </c>
       <c r="G24" t="n">
-        <v>407641</v>
+        <v>322945</v>
       </c>
       <c r="H24" t="n">
-        <v>68689</v>
+        <v>65174</v>
       </c>
     </row>
     <row r="25">
@@ -1000,25 +1000,25 @@
         <v>45829</v>
       </c>
       <c r="B25" t="n">
-        <v>1544.94</v>
+        <v>1564.68</v>
       </c>
       <c r="C25" t="n">
         <v>24</v>
       </c>
       <c r="D25" t="n">
-        <v>1114.23</v>
+        <v>1136.23</v>
       </c>
       <c r="E25" t="n">
-        <v>306.26</v>
+        <v>319.44</v>
       </c>
       <c r="F25" t="n">
-        <v>2638</v>
+        <v>1623</v>
       </c>
       <c r="G25" t="n">
-        <v>396334</v>
+        <v>438012</v>
       </c>
       <c r="H25" t="n">
-        <v>64147</v>
+        <v>70405</v>
       </c>
     </row>
     <row r="26">
@@ -1026,25 +1026,25 @@
         <v>45830</v>
       </c>
       <c r="B26" t="n">
-        <v>1514.13</v>
+        <v>1457.34</v>
       </c>
       <c r="C26" t="n">
         <v>24</v>
       </c>
       <c r="D26" t="n">
-        <v>1108.33</v>
+        <v>1054.64</v>
       </c>
       <c r="E26" t="n">
-        <v>308.48</v>
+        <v>292.97</v>
       </c>
       <c r="F26" t="n">
-        <v>2129</v>
+        <v>1721</v>
       </c>
       <c r="G26" t="n">
-        <v>409137</v>
+        <v>403122</v>
       </c>
       <c r="H26" t="n">
-        <v>70536</v>
+        <v>63930</v>
       </c>
     </row>
     <row r="27">
@@ -1052,25 +1052,25 @@
         <v>45831</v>
       </c>
       <c r="B27" t="n">
-        <v>1447.49</v>
+        <v>1505.11</v>
       </c>
       <c r="C27" t="n">
         <v>24</v>
       </c>
       <c r="D27" t="n">
-        <v>1054.88</v>
+        <v>1082.85</v>
       </c>
       <c r="E27" t="n">
-        <v>280.12</v>
+        <v>297.09</v>
       </c>
       <c r="F27" t="n">
-        <v>2127</v>
+        <v>1293</v>
       </c>
       <c r="G27" t="n">
-        <v>391932</v>
+        <v>379954</v>
       </c>
       <c r="H27" t="n">
-        <v>66308</v>
+        <v>73086</v>
       </c>
     </row>
     <row r="28">
@@ -1078,25 +1078,25 @@
         <v>45832</v>
       </c>
       <c r="B28" t="n">
-        <v>1596.69</v>
+        <v>1442.96</v>
       </c>
       <c r="C28" t="n">
-        <v>24</v>
+        <v>23.37</v>
       </c>
       <c r="D28" t="n">
-        <v>1162.68</v>
+        <v>1034.86</v>
       </c>
       <c r="E28" t="n">
-        <v>306.33</v>
+        <v>279.6</v>
       </c>
       <c r="F28" t="n">
-        <v>2892</v>
+        <v>1385</v>
       </c>
       <c r="G28" t="n">
-        <v>428181</v>
+        <v>364063</v>
       </c>
       <c r="H28" t="n">
-        <v>66081</v>
+        <v>65201</v>
       </c>
     </row>
     <row r="29">
@@ -1104,25 +1104,25 @@
         <v>45833</v>
       </c>
       <c r="B29" t="n">
-        <v>1565.45</v>
+        <v>1397.17</v>
       </c>
       <c r="C29" t="n">
-        <v>24</v>
+        <v>21.99</v>
       </c>
       <c r="D29" t="n">
-        <v>1128.35</v>
+        <v>1012.86</v>
       </c>
       <c r="E29" t="n">
-        <v>313.73</v>
+        <v>279.43</v>
       </c>
       <c r="F29" t="n">
-        <v>2356</v>
+        <v>1457</v>
       </c>
       <c r="G29" t="n">
-        <v>421892</v>
+        <v>347396</v>
       </c>
       <c r="H29" t="n">
-        <v>70090</v>
+        <v>64974</v>
       </c>
     </row>
     <row r="30">
@@ -1130,25 +1130,25 @@
         <v>45834</v>
       </c>
       <c r="B30" t="n">
-        <v>1494.75</v>
+        <v>1422.25</v>
       </c>
       <c r="C30" t="n">
         <v>24</v>
       </c>
       <c r="D30" t="n">
-        <v>1082.89</v>
+        <v>1032.68</v>
       </c>
       <c r="E30" t="n">
-        <v>300.26</v>
+        <v>275.1</v>
       </c>
       <c r="F30" t="n">
-        <v>2309</v>
+        <v>1347</v>
       </c>
       <c r="G30" t="n">
-        <v>392898</v>
+        <v>406102</v>
       </c>
       <c r="H30" t="n">
-        <v>67406</v>
+        <v>66260</v>
       </c>
     </row>
     <row r="31">
@@ -1156,25 +1156,25 @@
         <v>45835</v>
       </c>
       <c r="B31" t="n">
-        <v>1248.79</v>
+        <v>1529.81</v>
       </c>
       <c r="C31" t="n">
-        <v>18.96</v>
+        <v>24</v>
       </c>
       <c r="D31" t="n">
-        <v>904.4400000000001</v>
+        <v>1127.24</v>
       </c>
       <c r="E31" t="n">
-        <v>255.14</v>
+        <v>305.73</v>
       </c>
       <c r="F31" t="n">
-        <v>2612</v>
+        <v>1374</v>
       </c>
       <c r="G31" t="n">
-        <v>339297</v>
+        <v>416062</v>
       </c>
       <c r="H31" t="n">
-        <v>53845</v>
+        <v>69571</v>
       </c>
     </row>
     <row r="32">
@@ -1182,25 +1182,25 @@
         <v>45836</v>
       </c>
       <c r="B32" t="n">
-        <v>1395.08</v>
+        <v>1429.93</v>
       </c>
       <c r="C32" t="n">
-        <v>21.45</v>
+        <v>24</v>
       </c>
       <c r="D32" t="n">
-        <v>1010.19</v>
+        <v>1042.72</v>
       </c>
       <c r="E32" t="n">
-        <v>274.02</v>
+        <v>285.12</v>
       </c>
       <c r="F32" t="n">
-        <v>2122</v>
+        <v>1354</v>
       </c>
       <c r="G32" t="n">
-        <v>355913</v>
+        <v>394600</v>
       </c>
       <c r="H32" t="n">
-        <v>65034</v>
+        <v>65322</v>
       </c>
     </row>
     <row r="33">
@@ -1208,25 +1208,25 @@
         <v>45837</v>
       </c>
       <c r="B33" t="n">
-        <v>907.23</v>
+        <v>1411.58</v>
       </c>
       <c r="C33" t="n">
-        <v>14.09</v>
+        <v>23.38</v>
       </c>
       <c r="D33" t="n">
-        <v>663.0599999999999</v>
+        <v>1024.55</v>
       </c>
       <c r="E33" t="n">
-        <v>179.08</v>
+        <v>278</v>
       </c>
       <c r="F33" t="n">
-        <v>1388</v>
+        <v>1191</v>
       </c>
       <c r="G33" t="n">
-        <v>256702</v>
+        <v>359918</v>
       </c>
       <c r="H33" t="n">
-        <v>38242</v>
+        <v>60834</v>
       </c>
     </row>
     <row r="34">
@@ -1234,25 +1234,25 @@
         <v>45838</v>
       </c>
       <c r="B34" t="n">
-        <v>628.48</v>
+        <v>1477.57</v>
       </c>
       <c r="C34" t="n">
-        <v>10.15</v>
+        <v>24</v>
       </c>
       <c r="D34" t="n">
-        <v>454.85</v>
+        <v>1075.48</v>
       </c>
       <c r="E34" t="n">
-        <v>122.55</v>
+        <v>295.45</v>
       </c>
       <c r="F34" t="n">
-        <v>1147</v>
+        <v>1522</v>
       </c>
       <c r="G34" t="n">
-        <v>190774</v>
+        <v>415576</v>
       </c>
       <c r="H34" t="n">
-        <v>30267</v>
+        <v>66350</v>
       </c>
     </row>
     <row r="36">
@@ -1262,25 +1262,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>40073.02000000001</v>
+        <v>34636.59</v>
       </c>
       <c r="C36" t="n">
-        <v>639.35</v>
+        <v>559.92</v>
       </c>
       <c r="D36" t="n">
-        <v>29083.48999999999</v>
+        <v>25118.09</v>
       </c>
       <c r="E36" t="n">
-        <v>7948.239999999999</v>
+        <v>6876.35</v>
       </c>
       <c r="F36" t="n">
-        <v>62945</v>
+        <v>33717</v>
       </c>
       <c r="G36" t="n">
-        <v>10777344</v>
+        <v>9180818</v>
       </c>
       <c r="H36" t="n">
-        <v>1788522</v>
+        <v>1572503</v>
       </c>
     </row>
   </sheetData>

--- a/00-esmagadora-modelo/dados_sujos/apontamentos_mensais/producao_2025_06.xlsx
+++ b/00-esmagadora-modelo/dados_sujos/apontamentos_mensais/producao_2025_06.xlsx
@@ -480,25 +480,25 @@
         <v>45809</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1426.9</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>23.19</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1042.87</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>290.26</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1341</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>386800</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>62352</v>
       </c>
     </row>
     <row r="6">
@@ -506,25 +506,25 @@
         <v>45810</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>1193.64</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>20.88</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>862.04</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>234.22</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1256</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>312152</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>52517</v>
       </c>
     </row>
     <row r="7">
@@ -532,25 +532,25 @@
         <v>45811</v>
       </c>
       <c r="B7" t="n">
-        <v>1519.66</v>
+        <v>1509.17</v>
       </c>
       <c r="C7" t="n">
         <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>1111.22</v>
+        <v>1097.49</v>
       </c>
       <c r="E7" t="n">
-        <v>300.83</v>
+        <v>300.1</v>
       </c>
       <c r="F7" t="n">
-        <v>1338</v>
+        <v>1855</v>
       </c>
       <c r="G7" t="n">
-        <v>379135</v>
+        <v>363541</v>
       </c>
       <c r="H7" t="n">
-        <v>70932</v>
+        <v>68436</v>
       </c>
     </row>
     <row r="8">
@@ -558,25 +558,25 @@
         <v>45812</v>
       </c>
       <c r="B8" t="n">
-        <v>1332.93</v>
+        <v>1550.36</v>
       </c>
       <c r="C8" t="n">
-        <v>21.84</v>
+        <v>24</v>
       </c>
       <c r="D8" t="n">
-        <v>969.83</v>
+        <v>1134.66</v>
       </c>
       <c r="E8" t="n">
-        <v>263.12</v>
+        <v>305.53</v>
       </c>
       <c r="F8" t="n">
-        <v>1157</v>
+        <v>1265</v>
       </c>
       <c r="G8" t="n">
-        <v>343074</v>
+        <v>384212</v>
       </c>
       <c r="H8" t="n">
-        <v>61225</v>
+        <v>70110</v>
       </c>
     </row>
     <row r="9">
@@ -584,25 +584,25 @@
         <v>45813</v>
       </c>
       <c r="B9" t="n">
-        <v>1179.81</v>
+        <v>1425.15</v>
       </c>
       <c r="C9" t="n">
-        <v>20.28</v>
+        <v>24</v>
       </c>
       <c r="D9" t="n">
-        <v>854.29</v>
+        <v>1042.47</v>
       </c>
       <c r="E9" t="n">
-        <v>235.69</v>
+        <v>285.01</v>
       </c>
       <c r="F9" t="n">
-        <v>881</v>
+        <v>1446</v>
       </c>
       <c r="G9" t="n">
-        <v>313655</v>
+        <v>428850</v>
       </c>
       <c r="H9" t="n">
-        <v>52437</v>
+        <v>65700</v>
       </c>
     </row>
     <row r="10">
@@ -610,25 +610,25 @@
         <v>45814</v>
       </c>
       <c r="B10" t="n">
-        <v>1418.72</v>
+        <v>1374.48</v>
       </c>
       <c r="C10" t="n">
-        <v>22.18</v>
+        <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>1021.17</v>
+        <v>1003.32</v>
       </c>
       <c r="E10" t="n">
-        <v>276.34</v>
+        <v>261.61</v>
       </c>
       <c r="F10" t="n">
-        <v>1357</v>
+        <v>1339</v>
       </c>
       <c r="G10" t="n">
-        <v>373572</v>
+        <v>360604</v>
       </c>
       <c r="H10" t="n">
-        <v>68608</v>
+        <v>57063</v>
       </c>
     </row>
     <row r="11">
@@ -636,25 +636,25 @@
         <v>45815</v>
       </c>
       <c r="B11" t="n">
-        <v>1530.11</v>
+        <v>1516.81</v>
       </c>
       <c r="C11" t="n">
         <v>24</v>
       </c>
       <c r="D11" t="n">
-        <v>1105.14</v>
+        <v>1101.41</v>
       </c>
       <c r="E11" t="n">
-        <v>310.53</v>
+        <v>306.99</v>
       </c>
       <c r="F11" t="n">
-        <v>1594</v>
+        <v>1348</v>
       </c>
       <c r="G11" t="n">
-        <v>392100</v>
+        <v>423449</v>
       </c>
       <c r="H11" t="n">
-        <v>65659</v>
+        <v>67531</v>
       </c>
     </row>
     <row r="12">
@@ -662,25 +662,25 @@
         <v>45816</v>
       </c>
       <c r="B12" t="n">
-        <v>938.35</v>
+        <v>1410.51</v>
       </c>
       <c r="C12" t="n">
-        <v>14.8</v>
+        <v>23.27</v>
       </c>
       <c r="D12" t="n">
-        <v>685.04</v>
+        <v>1023.79</v>
       </c>
       <c r="E12" t="n">
-        <v>179.99</v>
+        <v>276.53</v>
       </c>
       <c r="F12" t="n">
-        <v>912</v>
+        <v>1243</v>
       </c>
       <c r="G12" t="n">
-        <v>251344</v>
+        <v>375281</v>
       </c>
       <c r="H12" t="n">
-        <v>42474</v>
+        <v>64570</v>
       </c>
     </row>
     <row r="13">
@@ -688,25 +688,25 @@
         <v>45817</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1394.52</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1014</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>273.63</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1329</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>390324</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>65913</v>
       </c>
     </row>
     <row r="14">
@@ -714,25 +714,25 @@
         <v>45818</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1343.43</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>22.32</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>972.46</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>264.96</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1049</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>353899</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>56376</v>
       </c>
     </row>
     <row r="15">
@@ -740,25 +740,25 @@
         <v>45819</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>1390.42</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1007.61</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>284.02</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1507</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>376361</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>63222</v>
       </c>
     </row>
     <row r="16">
@@ -766,25 +766,25 @@
         <v>45820</v>
       </c>
       <c r="B16" t="n">
-        <v>1429.17</v>
+        <v>1362.83</v>
       </c>
       <c r="C16" t="n">
-        <v>24</v>
+        <v>21.48</v>
       </c>
       <c r="D16" t="n">
-        <v>1036.39</v>
+        <v>1000.04</v>
       </c>
       <c r="E16" t="n">
-        <v>284.34</v>
+        <v>270.53</v>
       </c>
       <c r="F16" t="n">
-        <v>1622</v>
+        <v>1508</v>
       </c>
       <c r="G16" t="n">
-        <v>397010</v>
+        <v>351925</v>
       </c>
       <c r="H16" t="n">
-        <v>58509</v>
+        <v>62106</v>
       </c>
     </row>
     <row r="17">
@@ -792,25 +792,25 @@
         <v>45821</v>
       </c>
       <c r="B17" t="n">
-        <v>1481.32</v>
+        <v>1348.44</v>
       </c>
       <c r="C17" t="n">
         <v>24</v>
       </c>
       <c r="D17" t="n">
-        <v>1079.29</v>
+        <v>985.64</v>
       </c>
       <c r="E17" t="n">
-        <v>293.74</v>
+        <v>267.56</v>
       </c>
       <c r="F17" t="n">
-        <v>1793</v>
+        <v>1450</v>
       </c>
       <c r="G17" t="n">
-        <v>383562</v>
+        <v>371082</v>
       </c>
       <c r="H17" t="n">
-        <v>65484</v>
+        <v>62402</v>
       </c>
     </row>
     <row r="18">
@@ -818,25 +818,25 @@
         <v>45822</v>
       </c>
       <c r="B18" t="n">
-        <v>1346.93</v>
+        <v>1270.38</v>
       </c>
       <c r="C18" t="n">
-        <v>21.98</v>
+        <v>19.62</v>
       </c>
       <c r="D18" t="n">
-        <v>969.76</v>
+        <v>920.84</v>
       </c>
       <c r="E18" t="n">
-        <v>268.52</v>
+        <v>257.14</v>
       </c>
       <c r="F18" t="n">
-        <v>1430</v>
+        <v>1581</v>
       </c>
       <c r="G18" t="n">
-        <v>372163</v>
+        <v>354872</v>
       </c>
       <c r="H18" t="n">
-        <v>60660</v>
+        <v>53362</v>
       </c>
     </row>
     <row r="19">
@@ -844,25 +844,25 @@
         <v>45823</v>
       </c>
       <c r="B19" t="n">
-        <v>1478.93</v>
+        <v>1435.78</v>
       </c>
       <c r="C19" t="n">
-        <v>23.07</v>
+        <v>23.46</v>
       </c>
       <c r="D19" t="n">
-        <v>1071.95</v>
+        <v>1039.77</v>
       </c>
       <c r="E19" t="n">
-        <v>294.41</v>
+        <v>281.98</v>
       </c>
       <c r="F19" t="n">
-        <v>1358</v>
+        <v>1572</v>
       </c>
       <c r="G19" t="n">
-        <v>395093</v>
+        <v>366296</v>
       </c>
       <c r="H19" t="n">
-        <v>66321</v>
+        <v>63718</v>
       </c>
     </row>
     <row r="20">
@@ -870,25 +870,25 @@
         <v>45824</v>
       </c>
       <c r="B20" t="n">
-        <v>1483.94</v>
+        <v>1104.28</v>
       </c>
       <c r="C20" t="n">
-        <v>24</v>
+        <v>17.35</v>
       </c>
       <c r="D20" t="n">
-        <v>1075.25</v>
+        <v>802.38</v>
       </c>
       <c r="E20" t="n">
-        <v>290.85</v>
+        <v>215.26</v>
       </c>
       <c r="F20" t="n">
-        <v>1421</v>
+        <v>1314</v>
       </c>
       <c r="G20" t="n">
-        <v>410707</v>
+        <v>300851</v>
       </c>
       <c r="H20" t="n">
-        <v>69345</v>
+        <v>49998</v>
       </c>
     </row>
     <row r="21">
@@ -896,25 +896,25 @@
         <v>45825</v>
       </c>
       <c r="B21" t="n">
-        <v>1318.75</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>21.71</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>952.34</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>265.19</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>1464</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>344633</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>56816</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -922,25 +922,25 @@
         <v>45826</v>
       </c>
       <c r="B22" t="n">
-        <v>1488.38</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>1074.18</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>293.84</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>1284</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>379680</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>70083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -948,25 +948,25 @@
         <v>45827</v>
       </c>
       <c r="B23" t="n">
-        <v>750.73</v>
+        <v>737.5</v>
       </c>
       <c r="C23" t="n">
         <v>12.48</v>
       </c>
       <c r="D23" t="n">
-        <v>540.22</v>
+        <v>530.96</v>
       </c>
       <c r="E23" t="n">
-        <v>149.43</v>
+        <v>145.09</v>
       </c>
       <c r="F23" t="n">
-        <v>722</v>
+        <v>2059</v>
       </c>
       <c r="G23" t="n">
-        <v>197340</v>
+        <v>205360</v>
       </c>
       <c r="H23" t="n">
-        <v>32843</v>
+        <v>33368</v>
       </c>
     </row>
     <row r="24">
@@ -974,25 +974,25 @@
         <v>45828</v>
       </c>
       <c r="B24" t="n">
-        <v>1300.46</v>
+        <v>1410.63</v>
       </c>
       <c r="C24" t="n">
-        <v>20.84</v>
+        <v>23.51</v>
       </c>
       <c r="D24" t="n">
-        <v>947.91</v>
+        <v>1026.18</v>
       </c>
       <c r="E24" t="n">
-        <v>261.6</v>
+        <v>281.31</v>
       </c>
       <c r="F24" t="n">
-        <v>1117</v>
+        <v>1282</v>
       </c>
       <c r="G24" t="n">
-        <v>322945</v>
+        <v>381137</v>
       </c>
       <c r="H24" t="n">
-        <v>65174</v>
+        <v>67027</v>
       </c>
     </row>
     <row r="25">
@@ -1000,25 +1000,25 @@
         <v>45829</v>
       </c>
       <c r="B25" t="n">
-        <v>1564.68</v>
+        <v>1550.23</v>
       </c>
       <c r="C25" t="n">
         <v>24</v>
       </c>
       <c r="D25" t="n">
-        <v>1136.23</v>
+        <v>1123.53</v>
       </c>
       <c r="E25" t="n">
-        <v>319.44</v>
+        <v>309.82</v>
       </c>
       <c r="F25" t="n">
-        <v>1623</v>
+        <v>1361</v>
       </c>
       <c r="G25" t="n">
-        <v>438012</v>
+        <v>377262</v>
       </c>
       <c r="H25" t="n">
-        <v>70405</v>
+        <v>72386</v>
       </c>
     </row>
     <row r="26">
@@ -1026,25 +1026,25 @@
         <v>45830</v>
       </c>
       <c r="B26" t="n">
-        <v>1457.34</v>
+        <v>1439.92</v>
       </c>
       <c r="C26" t="n">
         <v>24</v>
       </c>
       <c r="D26" t="n">
-        <v>1054.64</v>
+        <v>1043.3</v>
       </c>
       <c r="E26" t="n">
-        <v>292.97</v>
+        <v>281.49</v>
       </c>
       <c r="F26" t="n">
-        <v>1721</v>
+        <v>1249</v>
       </c>
       <c r="G26" t="n">
-        <v>403122</v>
+        <v>377062</v>
       </c>
       <c r="H26" t="n">
-        <v>63930</v>
+        <v>65509</v>
       </c>
     </row>
     <row r="27">
@@ -1052,25 +1052,25 @@
         <v>45831</v>
       </c>
       <c r="B27" t="n">
-        <v>1505.11</v>
+        <v>1439.79</v>
       </c>
       <c r="C27" t="n">
         <v>24</v>
       </c>
       <c r="D27" t="n">
-        <v>1082.85</v>
+        <v>1057.42</v>
       </c>
       <c r="E27" t="n">
-        <v>297.09</v>
+        <v>278.86</v>
       </c>
       <c r="F27" t="n">
-        <v>1293</v>
+        <v>1379</v>
       </c>
       <c r="G27" t="n">
-        <v>379954</v>
+        <v>364531</v>
       </c>
       <c r="H27" t="n">
-        <v>73086</v>
+        <v>69358</v>
       </c>
     </row>
     <row r="28">
@@ -1078,25 +1078,25 @@
         <v>45832</v>
       </c>
       <c r="B28" t="n">
-        <v>1442.96</v>
+        <v>775.37</v>
       </c>
       <c r="C28" t="n">
-        <v>23.37</v>
+        <v>12.75</v>
       </c>
       <c r="D28" t="n">
-        <v>1034.86</v>
+        <v>563.8099999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>279.6</v>
+        <v>156.3</v>
       </c>
       <c r="F28" t="n">
-        <v>1385</v>
+        <v>888</v>
       </c>
       <c r="G28" t="n">
-        <v>364063</v>
+        <v>214506</v>
       </c>
       <c r="H28" t="n">
-        <v>65201</v>
+        <v>34813</v>
       </c>
     </row>
     <row r="29">
@@ -1104,25 +1104,25 @@
         <v>45833</v>
       </c>
       <c r="B29" t="n">
-        <v>1397.17</v>
+        <v>1508.98</v>
       </c>
       <c r="C29" t="n">
-        <v>21.99</v>
+        <v>24</v>
       </c>
       <c r="D29" t="n">
-        <v>1012.86</v>
+        <v>1098.13</v>
       </c>
       <c r="E29" t="n">
-        <v>279.43</v>
+        <v>300.76</v>
       </c>
       <c r="F29" t="n">
-        <v>1457</v>
+        <v>1510</v>
       </c>
       <c r="G29" t="n">
-        <v>347396</v>
+        <v>380775</v>
       </c>
       <c r="H29" t="n">
-        <v>64974</v>
+        <v>66227</v>
       </c>
     </row>
     <row r="30">
@@ -1130,25 +1130,25 @@
         <v>45834</v>
       </c>
       <c r="B30" t="n">
-        <v>1422.25</v>
+        <v>1462.2</v>
       </c>
       <c r="C30" t="n">
         <v>24</v>
       </c>
       <c r="D30" t="n">
-        <v>1032.68</v>
+        <v>1061.83</v>
       </c>
       <c r="E30" t="n">
-        <v>275.1</v>
+        <v>294.47</v>
       </c>
       <c r="F30" t="n">
-        <v>1347</v>
+        <v>1394</v>
       </c>
       <c r="G30" t="n">
-        <v>406102</v>
+        <v>371360</v>
       </c>
       <c r="H30" t="n">
-        <v>66260</v>
+        <v>65344</v>
       </c>
     </row>
     <row r="31">
@@ -1156,25 +1156,25 @@
         <v>45835</v>
       </c>
       <c r="B31" t="n">
-        <v>1529.81</v>
+        <v>1520.55</v>
       </c>
       <c r="C31" t="n">
         <v>24</v>
       </c>
       <c r="D31" t="n">
-        <v>1127.24</v>
+        <v>1094.34</v>
       </c>
       <c r="E31" t="n">
-        <v>305.73</v>
+        <v>307.38</v>
       </c>
       <c r="F31" t="n">
-        <v>1374</v>
+        <v>1325</v>
       </c>
       <c r="G31" t="n">
-        <v>416062</v>
+        <v>385958</v>
       </c>
       <c r="H31" t="n">
-        <v>69571</v>
+        <v>73707</v>
       </c>
     </row>
     <row r="32">
@@ -1182,25 +1182,25 @@
         <v>45836</v>
       </c>
       <c r="B32" t="n">
-        <v>1429.93</v>
+        <v>1406.68</v>
       </c>
       <c r="C32" t="n">
-        <v>24</v>
+        <v>22.68</v>
       </c>
       <c r="D32" t="n">
-        <v>1042.72</v>
+        <v>1026.82</v>
       </c>
       <c r="E32" t="n">
-        <v>285.12</v>
+        <v>283.16</v>
       </c>
       <c r="F32" t="n">
-        <v>1354</v>
+        <v>1385</v>
       </c>
       <c r="G32" t="n">
-        <v>394600</v>
+        <v>384912</v>
       </c>
       <c r="H32" t="n">
-        <v>65322</v>
+        <v>60758</v>
       </c>
     </row>
     <row r="33">
@@ -1208,25 +1208,25 @@
         <v>45837</v>
       </c>
       <c r="B33" t="n">
-        <v>1411.58</v>
+        <v>1298.37</v>
       </c>
       <c r="C33" t="n">
-        <v>23.38</v>
+        <v>20.13</v>
       </c>
       <c r="D33" t="n">
-        <v>1024.55</v>
+        <v>936.33</v>
       </c>
       <c r="E33" t="n">
-        <v>278</v>
+        <v>257.38</v>
       </c>
       <c r="F33" t="n">
-        <v>1191</v>
+        <v>1125</v>
       </c>
       <c r="G33" t="n">
-        <v>359918</v>
+        <v>348938</v>
       </c>
       <c r="H33" t="n">
-        <v>60834</v>
+        <v>53695</v>
       </c>
     </row>
     <row r="34">
@@ -1234,25 +1234,25 @@
         <v>45838</v>
       </c>
       <c r="B34" t="n">
-        <v>1477.57</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>1075.48</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>295.45</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>1522</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>415576</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>66350</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1262,25 +1262,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>34636.59</v>
+        <v>36607.32000000001</v>
       </c>
       <c r="C36" t="n">
-        <v>559.92</v>
+        <v>599.12</v>
       </c>
       <c r="D36" t="n">
-        <v>25118.09</v>
+        <v>26613.44000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>6876.35</v>
+        <v>7271.35</v>
       </c>
       <c r="F36" t="n">
-        <v>33717</v>
+        <v>37360</v>
       </c>
       <c r="G36" t="n">
-        <v>9180818</v>
+        <v>9692300</v>
       </c>
       <c r="H36" t="n">
-        <v>1572503</v>
+        <v>1647568</v>
       </c>
     </row>
   </sheetData>
